--- a/apps/be/reports/ImpactCocoa_Farmer_Coaching_Report_v3.xlsx
+++ b/apps/be/reports/ImpactCocoa_Farmer_Coaching_Report_v3.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="176">
   <si>
-    <t>ImpactCocoa  |  Individual Farmer Coaching Report  |  AgroEco Ghana</t>
+    <t>Think!Cocoa  |  Individual Farmer Coaching Report  |  Think!Data</t>
   </si>
   <si>
     <t>Total visits:</t>
@@ -295,10 +295,10 @@
 (sec_q)</t>
   </si>
   <si>
-    <t>Individual Farmer Coaching Report — Developer Specification  |  ImpactCocoa ERP</t>
+    <t>Individual Farmer Coaching Report — Developer Specification  |  Think!Cocoa ERP</t>
   </si>
   <si>
-    <t>Specification for Brian To (Ondora Global JSC) to implement the Individual Farmer Coaching Report in the ImpactCocoa ERP. Source form: Farmer_Coaching_XLSForm_1.xlsx (IMP-COACH).</t>
+    <t>Specification for Brian To (Ondora Global JSC) to implement the Individual Farmer Coaching Report in the Think!Cocoa ERP. Source form: Farmer_Coaching_XLSForm_1.xlsx (IMP-COACH).</t>
   </si>
   <si>
     <t>1.  REPORT OVERVIEW</t>
